--- a/Hardware/LoadBoard_250W/JLC_PCBA_CPL-DALI_EVG_LoadBoard(V0.1).xlsx
+++ b/Hardware/LoadBoard_250W/JLC_PCBA_CPL-DALI_EVG_LoadBoard(V0.1).xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>10.095</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>KF2EDGR-3.81-4Pin</t>
+          <t>KF2EDGR-3.81-5Pin</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>CONN-TH_4P-P3.81_KF2EDGR-3.81-4P</t>
+          <t>CONN-TH_5P-P3.81_KF2EDGR-3.81-5P</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr">
